--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-OperationOutcome.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-OperationOutcome.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="257">
   <si>
     <t>Property</t>
   </si>
@@ -491,6 +491,16 @@
   </si>
   <si>
     <t>Meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
   </si>
   <si>
     <t>OperationOutcome.meta.tag</t>
@@ -1161,7 +1171,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="217.1875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="48.5546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2454,24 +2464,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2497,13 +2507,13 @@
         <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2529,13 +2539,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2553,7 +2563,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2562,24 +2572,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2605,13 +2615,13 @@
         <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2661,7 +2671,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2684,10 +2694,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2710,16 +2720,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2745,13 +2755,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -2769,7 +2779,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2792,14 +2802,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2818,16 +2828,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2877,7 +2887,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2892,7 +2902,7 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -2900,14 +2910,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2926,16 +2936,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2985,7 +2995,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3000,7 +3010,7 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3008,10 +3018,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3040,7 +3050,7 @@
         <v>107</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>109</v>
@@ -3081,19 +3091,19 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3108,7 +3118,7 @@
         <v>114</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3116,10 +3126,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3145,16 +3155,16 @@
         <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3191,19 +3201,19 @@
         <v>75</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3218,7 +3228,7 @@
         <v>114</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>75</v>
@@ -3226,10 +3236,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3252,13 +3262,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3309,7 +3319,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -3318,24 +3328,24 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3438,10 +3448,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3511,16 +3521,16 @@
         <v>75</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>113</v>
@@ -3546,14 +3556,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3575,16 +3585,16 @@
         <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -3633,7 +3643,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3648,7 +3658,7 @@
         <v>114</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -3656,10 +3666,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3682,19 +3692,19 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -3719,13 +3729,13 @@
         <v>75</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>75</v>
@@ -3743,7 +3753,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>85</v>
@@ -3758,18 +3768,18 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3792,17 +3802,17 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -3827,13 +3837,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -3851,7 +3861,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>85</v>
@@ -3866,18 +3876,18 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3900,16 +3910,16 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3935,11 +3945,11 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -3957,7 +3967,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3966,24 +3976,24 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4009,13 +4019,13 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4065,7 +4075,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4080,18 +4090,18 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4117,16 +4127,16 @@
         <v>99</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4175,7 +4185,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4190,18 +4200,18 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4227,16 +4237,16 @@
         <v>99</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4285,7 +4295,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4300,10 +4310,10 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-OperationOutcome.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-OperationOutcome.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="254">
   <si>
     <t>Property</t>
   </si>
@@ -491,16 +491,6 @@
   </si>
   <si>
     <t>Meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
   </si>
   <si>
     <t>OperationOutcome.meta.tag</t>
@@ -1171,7 +1161,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="217.1875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2464,24 +2454,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2507,13 +2497,13 @@
         <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2539,31 +2529,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2572,24 +2562,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2615,13 +2605,13 @@
         <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2671,7 +2661,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2694,10 +2684,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2720,16 +2710,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2755,31 +2745,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2802,14 +2792,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2828,16 +2818,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2887,7 +2877,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2902,7 +2892,7 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -2910,14 +2900,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2936,16 +2926,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2995,7 +2985,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3010,7 +3000,7 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3018,10 +3008,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3050,7 +3040,7 @@
         <v>107</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>109</v>
@@ -3091,19 +3081,19 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3118,7 +3108,7 @@
         <v>114</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3126,10 +3116,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3155,16 +3145,16 @@
         <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3201,19 +3191,19 @@
         <v>75</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3228,7 +3218,7 @@
         <v>114</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>75</v>
@@ -3236,10 +3226,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3262,13 +3252,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3319,7 +3309,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -3328,24 +3318,24 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3448,10 +3438,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3521,16 +3511,16 @@
         <v>75</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>113</v>
@@ -3556,14 +3546,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3585,16 +3575,16 @@
         <v>106</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>109</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -3643,7 +3633,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3658,7 +3648,7 @@
         <v>114</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -3666,10 +3656,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3692,19 +3682,19 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>75</v>
@@ -3729,13 +3719,13 @@
         <v>75</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>75</v>
@@ -3753,7 +3743,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>85</v>
@@ -3768,18 +3758,18 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3802,17 +3792,17 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -3837,13 +3827,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -3861,7 +3851,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>85</v>
@@ -3876,18 +3866,18 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3910,16 +3900,16 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3945,11 +3935,11 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -3967,7 +3957,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3976,24 +3966,24 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4019,13 +4009,13 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4075,7 +4065,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4090,18 +4080,18 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4127,16 +4117,16 @@
         <v>99</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O28" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4185,7 +4175,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4200,18 +4190,18 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4237,16 +4227,16 @@
         <v>99</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4295,7 +4285,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4310,10 +4300,10 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
